--- a/AAII_Financials/Yearly/QCRH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/QCRH_YR_FIN.xlsx
@@ -2981,7 +2981,7 @@
         <v>486700</v>
       </c>
       <c r="G58" s="3">
-        <v>711200</v>
+        <v>745300</v>
       </c>
       <c r="H58" s="3">
         <v>239900</v>
@@ -3083,7 +3083,7 @@
         <v>7000700</v>
       </c>
       <c r="G60" s="3">
-        <v>6695500</v>
+        <v>6729500</v>
       </c>
       <c r="H60" s="3">
         <v>5162600</v>
@@ -3134,7 +3134,7 @@
         <v>450900</v>
       </c>
       <c r="G61" s="3">
-        <v>318400</v>
+        <v>284300</v>
       </c>
       <c r="H61" s="3">
         <v>157400</v>
